--- a/data/df_modelling_full.xlsx
+++ b/data/df_modelling_full.xlsx
@@ -19820,7 +19820,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B329" t="n">
         <v>0</v>
